--- a/data/eval/auto_report.xlsx
+++ b/data/eval/auto_report.xlsx
@@ -7,59 +7,98 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Strategy" sheetId="2" r:id="rId2"/>
+    <sheet name="Lap Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Total Questions</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Accuracy (%)</t>
-  </si>
-  <si>
-    <t>Avg Latency (ms)</t>
-  </si>
-  <si>
-    <t>Max Latency (ms)</t>
-  </si>
-  <si>
-    <t>Min Latency (ms)</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>1-stop_time</t>
-  </si>
-  <si>
-    <t>2-stop_time</t>
-  </si>
-  <si>
-    <t>BestStrategy</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="28">
+  <si>
+    <t>lap</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>driver</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>lap_time</t>
   </si>
   <si>
     <t>VER</t>
   </si>
   <si>
-    <t>1-stop</t>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>RUS</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>ALO</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>PIA</t>
+  </si>
+  <si>
+    <t>HAM</t>
+  </si>
+  <si>
+    <t>HUL</t>
+  </si>
+  <si>
+    <t>TSU</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>RIC</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>BOT</t>
+  </si>
+  <si>
+    <t>ZHO</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>OCO</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -417,71 +456,1883 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>90.03100000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>128.726</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>90.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>102.855</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>89.374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>116.873</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>97.78700000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>89.42100000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>112.745</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>89.179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>119.683</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>91.26000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>111.926</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>90.24299999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>108.538</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>90.09399999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>107.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>89.16500000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>122.605</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>89.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>111.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>89.407</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>121.348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="E25">
+        <v>90.34999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26">
+        <v>124.72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27">
+        <v>129.967</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>90.69799999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>0</v>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>107.025</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30">
+        <v>89.922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>126.521</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>89.60299999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33">
+        <v>125.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34">
+        <v>89.485</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>129.274</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>91.208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37">
+        <v>119.562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>5</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38">
+        <v>89.90900000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>108.457</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>90.425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41">
+        <v>108.846</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42">
+        <v>89.57299999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43">
+        <v>112.447</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>89.608</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>115.236</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46">
+        <v>89.50700000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47">
+        <v>90.221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>122.063</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50">
+        <v>113.606</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51">
+        <v>89.932</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52">
+        <v>112.254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>127.938</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54">
+        <v>90.03</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>14</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55">
+        <v>107.564</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56">
+        <v>89.53700000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57">
+        <v>90.179</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58">
+        <v>124.55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59">
+        <v>113.925</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60">
+        <v>90.136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61">
+        <v>119.624</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62">
+        <v>89.801</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63">
+        <v>121.157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64">
+        <v>89.542</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>14</v>
+      </c>
+      <c r="C65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65">
+        <v>127.513</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66">
+        <v>90.143</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67">
+        <v>115.89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68">
+        <v>89.941</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69">
+        <v>114.087</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70">
+        <v>116.053</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71">
+        <v>89.679</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72">
+        <v>106.285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>14</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73">
+        <v>89.614</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>90.69199999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75">
+        <v>116.38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76">
+        <v>90.53100000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77">
+        <v>117.365</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>8</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78">
+        <v>90.624</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79">
+        <v>112.289</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80">
+        <v>90.122</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81">
+        <v>117.278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>14</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82">
+        <v>90.651</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>15</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83">
+        <v>108.367</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84">
+        <v>89.68300000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>2</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85">
+        <v>90.806</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>3</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86">
+        <v>115.826</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>5</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87">
+        <v>90.45099999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88">
+        <v>115.724</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>8</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89">
+        <v>90.363</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>9</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90">
+        <v>104.321</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91">
+        <v>89.718</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92">
+        <v>119.366</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>14</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93">
+        <v>90.44499999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>15</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94">
+        <v>107.151</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95">
+        <v>89.70999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>2</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96">
+        <v>90.623</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>3</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97">
+        <v>115.586</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98">
+        <v>90.566</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99">
+        <v>111.635</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>8</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100">
+        <v>90.997</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>9</v>
+      </c>
+      <c r="C101" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101">
+        <v>111.641</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102">
+        <v>89.851</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103">
+        <v>12</v>
+      </c>
+      <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103">
+        <v>112.113</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>14</v>
+      </c>
+      <c r="C104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104">
+        <v>90.502</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>15</v>
+      </c>
+      <c r="C105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105">
+        <v>105.117</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106">
+        <v>90.616</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>15</v>
+      </c>
+      <c r="E107">
+        <v>90.881</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>3</v>
+      </c>
+      <c r="C108" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108">
+        <v>111.134</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>5</v>
+      </c>
+      <c r="C109" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109">
+        <v>90.48099999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>6</v>
+      </c>
+      <c r="C110" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110">
+        <v>114.23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111">
+        <v>8</v>
+      </c>
+      <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="E111">
+        <v>91.102</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112">
+        <v>103.233</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>11</v>
+      </c>
+      <c r="C113" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113">
+        <v>90.129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>12</v>
+      </c>
+      <c r="C114" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114">
+        <v>115.713</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115">
+        <v>90.864</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116">
+        <v>108.264</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>5</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117">
+        <v>89.965</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118">
+        <v>117.189</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>8</v>
+      </c>
+      <c r="C119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119">
+        <v>90.982</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
+        <v>9</v>
+      </c>
+      <c r="C120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120">
+        <v>107.744</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>11</v>
+      </c>
+      <c r="C121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>12</v>
+      </c>
+      <c r="C122" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122">
+        <v>125.006</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123">
+        <v>90.69199999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124">
+        <v>116.649</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>5</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125">
+        <v>90.39700000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126">
+        <v>124.142</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
+        <v>8</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127">
+        <v>91.152</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128">
+        <v>106.67</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129">
+        <v>90.221</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130">
+        <v>127.201</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131">
+        <v>91.02500000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132">
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132">
+        <v>112.409</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133">
+        <v>5</v>
+      </c>
+      <c r="C133" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133">
+        <v>90.562</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134">
+        <v>111.968</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135">
+        <v>8</v>
+      </c>
+      <c r="C135" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135">
+        <v>91.126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>9</v>
+      </c>
+      <c r="C136" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136">
+        <v>108.368</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137">
+        <v>90.27800000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>12</v>
+      </c>
+      <c r="C138" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138">
+        <v>116.019</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139">
+        <v>91.252</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>3</v>
+      </c>
+      <c r="C140" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140">
+        <v>103.574</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>5</v>
+      </c>
+      <c r="C141" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141">
+        <v>90.646</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142">
+        <v>124.061</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143">
+        <v>8</v>
+      </c>
+      <c r="C143" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143">
+        <v>91.17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144">
+        <v>9</v>
+      </c>
+      <c r="C144" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144">
+        <v>106.691</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145">
+        <v>90.529</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146">
+        <v>12</v>
+      </c>
+      <c r="C146" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146">
+        <v>107.834</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>20</v>
+      </c>
+      <c r="E147">
+        <v>91.077</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148">
+        <v>3</v>
+      </c>
+      <c r="C148" t="s">
+        <v>20</v>
+      </c>
+      <c r="E148">
+        <v>112.534</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149">
+        <v>5</v>
+      </c>
+      <c r="C149" t="s">
+        <v>20</v>
+      </c>
+      <c r="E149">
+        <v>90.756</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150">
+        <v>6</v>
+      </c>
+      <c r="C150" t="s">
+        <v>20</v>
+      </c>
+      <c r="E150">
+        <v>126.222</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>21</v>
+      </c>
+      <c r="E151">
+        <v>91.075</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152">
+        <v>3</v>
+      </c>
+      <c r="C152" t="s">
+        <v>21</v>
+      </c>
+      <c r="E152">
+        <v>108.821</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153">
+        <v>5</v>
+      </c>
+      <c r="C153" t="s">
+        <v>21</v>
+      </c>
+      <c r="E153">
+        <v>90.75700000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>21</v>
+      </c>
+      <c r="E154">
+        <v>117.631</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>22</v>
+      </c>
+      <c r="E155">
+        <v>90.77</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156">
+        <v>3</v>
+      </c>
+      <c r="C156" t="s">
+        <v>22</v>
+      </c>
+      <c r="E156">
+        <v>114.6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157">
+        <v>5</v>
+      </c>
+      <c r="C157" t="s">
+        <v>22</v>
+      </c>
+      <c r="E157">
+        <v>91.128</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158">
+        <v>6</v>
+      </c>
+      <c r="C158" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158">
+        <v>119.862</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>23</v>
+      </c>
+      <c r="E159">
+        <v>91.98999999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160">
+        <v>115.505</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161">
+        <v>5</v>
+      </c>
+      <c r="C161" t="s">
+        <v>23</v>
+      </c>
+      <c r="E161">
+        <v>91.261</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162">
+        <v>6</v>
+      </c>
+      <c r="C162" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162">
+        <v>110.437</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163">
+        <v>8</v>
+      </c>
+      <c r="C163" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163">
+        <v>90.79300000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164">
+        <v>9</v>
+      </c>
+      <c r="C164" t="s">
+        <v>23</v>
+      </c>
+      <c r="E164">
+        <v>127.493</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165">
+        <v>2</v>
+      </c>
+      <c r="C165" t="s">
+        <v>24</v>
+      </c>
+      <c r="E165">
+        <v>92.434</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166">
+        <v>3</v>
+      </c>
+      <c r="C166" t="s">
+        <v>24</v>
+      </c>
+      <c r="E166">
+        <v>109.853</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167">
+        <v>5</v>
+      </c>
+      <c r="C167" t="s">
+        <v>24</v>
+      </c>
+      <c r="E167">
+        <v>91.28100000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168">
+        <v>6</v>
+      </c>
+      <c r="C168" t="s">
+        <v>24</v>
+      </c>
+      <c r="E168">
+        <v>109.747</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169">
+        <v>8</v>
+      </c>
+      <c r="C169" t="s">
+        <v>24</v>
+      </c>
+      <c r="E169">
+        <v>90.94799999999999</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170">
+        <v>9</v>
+      </c>
+      <c r="C170" t="s">
+        <v>24</v>
+      </c>
+      <c r="E170">
+        <v>122.15</v>
       </c>
     </row>
   </sheetData>
@@ -491,35 +2342,301 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>104.64</v>
+      </c>
+      <c r="C2">
+        <v>90.221</v>
+      </c>
+      <c r="D2">
+        <v>127.201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>107.381</v>
+      </c>
+      <c r="C3">
+        <v>89.542</v>
+      </c>
+      <c r="D3">
+        <v>127.513</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>105.147</v>
+      </c>
+      <c r="C4">
+        <v>90.756</v>
+      </c>
+      <c r="D4">
+        <v>126.222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>102.736</v>
+      </c>
+      <c r="C5">
+        <v>90.94799999999999</v>
+      </c>
+      <c r="D5">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>100.353</v>
+      </c>
+      <c r="C6">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="D6">
+        <v>119.366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>99.932</v>
+      </c>
+      <c r="C7">
+        <v>89.851</v>
+      </c>
+      <c r="D7">
+        <v>115.586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>101.916</v>
+      </c>
+      <c r="C8">
+        <v>89.16500000000001</v>
+      </c>
+      <c r="D8">
+        <v>122.605</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>100.72</v>
+      </c>
+      <c r="C9">
+        <v>90.529</v>
+      </c>
+      <c r="D9">
+        <v>124.061</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>101.462</v>
+      </c>
+      <c r="C10">
+        <v>89.614</v>
+      </c>
+      <c r="D10">
+        <v>116.053</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>104.58</v>
+      </c>
+      <c r="C11">
+        <v>90.79300000000001</v>
+      </c>
+      <c r="D11">
+        <v>127.493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B12">
+        <v>103.364</v>
+      </c>
+      <c r="C12">
+        <v>89.53700000000001</v>
+      </c>
+      <c r="D12">
+        <v>127.938</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>5588</v>
-      </c>
-      <c r="C2">
-        <v>5600</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
+      <c r="B13">
+        <v>101.271</v>
+      </c>
+      <c r="C13">
+        <v>89.68300000000001</v>
+      </c>
+      <c r="D13">
+        <v>117.365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>101.469</v>
+      </c>
+      <c r="C14">
+        <v>90.27800000000001</v>
+      </c>
+      <c r="D14">
+        <v>116.019</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>108.454</v>
+      </c>
+      <c r="C15">
+        <v>89.485</v>
+      </c>
+      <c r="D15">
+        <v>129.967</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>100.434</v>
+      </c>
+      <c r="C16">
+        <v>89.50700000000001</v>
+      </c>
+      <c r="D16">
+        <v>119.562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>104.09</v>
+      </c>
+      <c r="C17">
+        <v>90.77</v>
+      </c>
+      <c r="D17">
+        <v>119.862</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>102.527</v>
+      </c>
+      <c r="C18">
+        <v>89.965</v>
+      </c>
+      <c r="D18">
+        <v>125.006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>100.863</v>
+      </c>
+      <c r="C19">
+        <v>90.129</v>
+      </c>
+      <c r="D19">
+        <v>115.713</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>102.439</v>
+      </c>
+      <c r="C20">
+        <v>89.179</v>
+      </c>
+      <c r="D20">
+        <v>128.726</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>102.071</v>
+      </c>
+      <c r="C21">
+        <v>90.75700000000001</v>
+      </c>
+      <c r="D21">
+        <v>117.631</v>
       </c>
     </row>
   </sheetData>
